--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="Rc9ff1e18446f4403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R95a4d00e83a3455c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -339,28 +339,28 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次业务输入包含搜索查询事件、搜索运营归一化规则和合规敏感词表</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="32" customHeight="1">
+        <x:v>本次搜索发布批次的材料说明、查询事件、归一化规则、合规敏感词表和起始程序</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="60" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>原始输入文件</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>解压输入数据包后从input_data读取本地材料</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="46" customHeight="1">
+        <x:v>README.md；data/query_events.jsonl；data/normalization_rules.json；data/sensitive_terms.csv；starter/build_suggestions.mjs</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>发布目标</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>data/query_events.jsonl；data/normalization_rules.json；data/sensitive_terms.csv；starter/build_suggestions.mjs</x:v>
+        <x:v>形成中英文建议词排名，把敏感查询交给合规团队，并保留逐条词形与得分轨迹</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>output/build_suggestions.mjs；output/reports/suggestion_rankings.csv；output/reports/suppressed_queries.csv；output/reports/normalization_audit.csv</x:v>
@@ -368,98 +368,74 @@
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>交付用途</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>归一化查询；映射别名；压制敏感词；计算时间衰减；聚合语种与词形；排序建议词；输出三份业务结果</x:v>
+        <x:v>搜索服务使用排名表更新建议词，合规人员根据压制清单跟进分类，数据分析人员使用归一化轨迹核对词形与得分</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>业务目标</x:v>
+        <x:v>Node.js步骤</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>为搜索发布窗口准备中英文建议词排名，同时把敏感查询分流给合规团队，把逐条词形和得分轨迹交给数据分析人员</x:v>
+        <x:v>读取三份业务数据，完成Unicode词形处理、敏感词分流、时间衰减、语种聚合和排序，再写出完成程序与三份CSV</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>交付要求</x:v>
+        <x:v>词形处理</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>保存完成程序，并输出建议词排名、敏感查询压制清单和归一化轨迹三份CSV；三个业务交付之间可用event_id和canonical_query对应</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="46" customHeight="1">
+        <x:v>raw_query依次去除首尾空白、小写转换与Unicode连续空白折叠，再按aliases取得canonical_query</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>软件步骤</x:v>
+        <x:v>敏感词处置</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>Node.js读取三份输入，完成Unicode词形处理、敏感词分流、时间衰减、语种聚合和排序，再写出完成程序与三份CSV</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="46" customHeight="1">
+        <x:v>按词表顺序检查normalized_query和canonical_query，命中事件不进入排名来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>词形处理</x:v>
+        <x:v>热度计算</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>raw_query依次去除首尾空白、小写转换与Unicode连续空白折叠，再按aliases取得canonical_query</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="32" customHeight="1">
+        <x:v>天龄由规则参考时刻与事件时刻之差得到，衰减得分同时消费曝光、点击和半衰期参数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>敏感词处置</x:v>
+        <x:v>语种排名</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>按词表顺序检查normalized_query和canonical_query，命中事件不进入排名来源</x:v>
+        <x:v>按locale与canonical_query聚合，再用衰减得分、点击数和canonical_query代码点确定顺序</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>热度计算</x:v>
+        <x:v>结果对账</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>天龄由规则参考时刻与事件时刻之差得到，衰减得分同时消费曝光、点击和半衰期参数</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="46" customHeight="1">
+        <x:v>全部event_id出现在归一化轨迹，压制清单与轨迹状态一致，排名来源只来自未压制轨迹</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>语种排名</x:v>
+        <x:v>交付关联</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>按locale与canonical_query聚合，再用衰减得分、点击数和canonical_query代码点确定顺序</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="32" customHeight="1">
+        <x:v>三份业务结果可用event_id与canonical_query对应，压制事件不得进入排名来源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="46" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>业务关联</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>全部event_id出现在归一化轨迹，压制清单与轨迹状态一致，排名来源只来自未压制轨迹</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="46" customHeight="1">
-      <x:c r="A18" s="7" t="str">
-        <x:v>完成条件</x:v>
-      </x:c>
-      <x:c r="B18" s="7" t="str">
-        <x:v>Node.js入口正常结束，完成程序与三份CSV可读，event_id、canonical_query、压制分类和排名来源能够跨文件对应</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="32" customHeight="1">
-      <x:c r="A19" s="7" t="str">
-        <x:v>可验证点</x:v>
-      </x:c>
-      <x:c r="B19" s="7" t="str">
-        <x:v>归一化顺序、别名映射、敏感词命中、衰减得分、语种聚合和排名都能由本次业务输入逐项核对</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="32" customHeight="1">
-      <x:c r="A20" s="7" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B20" s="7" t="str">
-        <x:v>实现边界限于业务结果；函数拆分、内部容器、临时变量、CSV引用符、本机路径和源码注释可以不同</x:v>
+        <x:v>允许调整函数拆分、内部容器、临时变量、CSV引用符、本机路径和源码注释；输入主键、业务规则、字段含义与交付路径保持不变</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R95a4d00e83a3455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R71a41bfec3ff41f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -320,114 +320,114 @@
     </x:row>
     <x:row r="3" ht="32" customHeight="1">
       <x:c r="A3" s="7" t="str">
-        <x:v>主软件</x:v>
+        <x:v>建议词发布职责</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>Node.js</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="32" customHeight="1">
+        <x:v>搜索数据工程师整理本批次中英文查询事件，形成建议词排名，把敏感查询分流给合规团队，并保留逐条词形与得分轨迹。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="60" customHeight="1">
       <x:c r="A4" s="7" t="str">
-        <x:v>辅助工具</x:v>
+        <x:v>本次业务输入</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>npm、PowerShell或系统终端、CSV与JSON查看器</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="32" customHeight="1">
+        <x:v>query_events.jsonl保存查询、语种、曝光、点击与事件时刻；normalization_rules.json规定归一化、衰减和语种名额；sensitive_terms.csv是合规压制词表；starter/build_suggestions.mjs是待完成程序。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="46" customHeight="1">
       <x:c r="A5" s="7" t="str">
-        <x:v>输入来源</x:v>
+        <x:v>业务消费者</x:v>
       </x:c>
       <x:c r="B5" s="7" t="str">
-        <x:v>本次搜索发布批次的材料说明、查询事件、归一化规则、合规敏感词表和起始程序</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="60" customHeight="1">
+        <x:v>搜索服务导入suggestion_rankings.csv；合规人员查看suppressed_queries.csv跟进分类；数据分析人员使用normalization_audit.csv查看词形、压制状态和得分。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="46" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>Node.js处理入口</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
-        <x:v>README.md；data/query_events.jsonl；data/normalization_rules.json；data/sensitive_terms.csv；starter/build_suggestions.mjs</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="32" customHeight="1">
+        <x:v>在input_data目录执行npm run process。程序读取本地JSONL、JSON与CSV，将完成程序写到output，并把三份业务结果写到output/reports。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="46" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>发布目标</x:v>
+        <x:v>词形规整</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
-        <x:v>形成中英文建议词排名，把敏感查询交给合规团队，并保留逐条词形与得分轨迹</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="60" customHeight="1">
+        <x:v>raw_query依次去除首尾空白、转为小写并折叠Unicode连续空白，再用aliases取得canonical_query和映射状态。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="46" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>交付文件</x:v>
+        <x:v>敏感词分流</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
-        <x:v>output/build_suggestions.mjs；output/reports/suggestion_rankings.csv；output/reports/suppressed_queries.csv；output/reports/normalization_audit.csv</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="32" customHeight="1">
+        <x:v>按sensitive_terms.csv物理行序先检查normalized_query，再检查canonical_query；记录首个命中词、命中词形和分类，命中事件不进入排名来源。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="46" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>交付用途</x:v>
+        <x:v>事件热度</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
-        <x:v>搜索服务使用排名表更新建议词，合规人员根据压制清单跟进分类，数据分析人员使用归一化轨迹核对词形与得分</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="32" customHeight="1">
+        <x:v>用reference_time_utc和event_time_utc计算天龄，按decay_half_life_days取得衰减因子，并结合曝光、点击和click_boost算出event_score。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="46" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>Node.js步骤</x:v>
+        <x:v>语种内聚合</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>读取三份业务数据，完成Unicode词形处理、敏感词分流、时间衰减、语种聚合和排序，再写出完成程序与三份CSV</x:v>
+        <x:v>未压制事件按locale和canonical_query汇总曝光、点击、衰减得分、来源event_id、别名事件数量和最新事件时刻。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="46" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>词形处理</x:v>
+        <x:v>建议词排序</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
-        <x:v>raw_query依次去除首尾空白、小写转换与Unicode连续空白折叠，再按aliases取得canonical_query</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="32" customHeight="1">
+        <x:v>每个locale先按decayed_score降序，再按total_clicks降序和canonical_query代码点升序取top_n_per_locale，rank从1连续编号。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="46" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>敏感词处置</x:v>
+        <x:v>归一化轨迹</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
-        <x:v>按词表顺序检查normalized_query和canonical_query，命中事件不进入排名来源</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="32" customHeight="1">
+        <x:v>query_events.jsonl中的每个event_id在normalization_audit.csv恰有一行，保存原始词、规整词、canonical_query、映射状态、压制信息和事件得分。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="46" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>热度计算</x:v>
+        <x:v>压制清单</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
-        <x:v>天龄由规则参考时刻与事件时刻之差得到，衰减得分同时消费曝光、点击和半衰期参数</x:v>
+        <x:v>suppressed_queries.csv只收录压制事件，保留event_id、命中词、命中词形、分类和remove_from_suggestions处置动作。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="46" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>语种排名</x:v>
+        <x:v>建议词排名</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
-        <x:v>按locale与canonical_query聚合，再用衰减得分、点击数和canonical_query代码点确定顺序</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="32" customHeight="1">
+        <x:v>suggestion_rankings.csv只聚合未压制事件，保留locale、rank、canonical_query、汇总数值、来源event_id和最新事件时刻。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="46" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>结果对账</x:v>
+        <x:v>跨表关系</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
-        <x:v>全部event_id出现在归一化轨迹，压制清单与轨迹状态一致，排名来源只来自未压制轨迹</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="32" customHeight="1">
+        <x:v>轨迹覆盖全部输入事件；压制清单等于轨迹中的压制事件；排名来源恰好来自未压制轨迹，三份结果可用event_id、locale和canonical_query关联。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>交付关联</x:v>
+        <x:v>交付目录</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
-        <x:v>三份业务结果可用event_id与canonical_query对应，压制事件不得进入排名来源</x:v>
+        <x:v>交付output/build_suggestions.mjs、output/reports/suggestion_rankings.csv、output/reports/suppressed_queries.csv和output/reports/normalization_audit.csv。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="46" customHeight="1">
@@ -435,7 +435,7 @@
         <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
-        <x:v>允许调整函数拆分、内部容器、临时变量、CSV引用符、本机路径和源码注释；输入主键、业务规则、字段含义与交付路径保持不变</x:v>
+        <x:v>允许调整函数拆分、内部容器、临时变量、CSV引用符、本机路径和源码注释；输入主键、业务规则、字段含义及交付路径不得变化。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
